--- a/resultados/ubirata/inventario_externos.xlsx
+++ b/resultados/ubirata/inventario_externos.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G45"/>
+  <dimension ref="A1:G49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,17 +461,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia-api/api/files/arquivo/69582</t>
+          <t>https://leismunicipais.com.br/prefeitura/pr/ubirata</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>leismunicipais.com.br</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Organograma</t>
+          <t>Leis Municipais</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -484,7 +484,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 18:58:42</t>
         </is>
       </c>
     </row>
@@ -496,19 +496,15 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/</t>
+          <t>https://www.facebook.com/prefeituraubirata/</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Portal da Transparência</t>
-        </is>
-      </c>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>https://www.ubirata.pr.gov.br/</t>
@@ -519,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 18:58:42</t>
         </is>
       </c>
     </row>
@@ -531,19 +527,15 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
+          <t>https://www.instagram.com/prefeituraubirata/</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Governo Digital Serviços Online</t>
-        </is>
-      </c>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>https://www.ubirata.pr.gov.br/</t>
@@ -554,7 +546,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 18:58:42</t>
         </is>
       </c>
     </row>
@@ -566,19 +558,15 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servidor</t>
+          <t>https://www.elotech.com.br</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Portal do Servidor</t>
-        </is>
-      </c>
+          <t>www.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>https://www.ubirata.pr.gov.br/</t>
@@ -589,7 +577,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 18:58:42</t>
         </is>
       </c>
     </row>
@@ -601,30 +589,30 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/cidadao</t>
+          <t>https://www.vlibras.gov.br/</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>www.vlibras.gov.br</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Portal do Cidadão</t>
+          <t>VLibras</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://www.ubirata.pr.gov.br/acessibilidade</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:00:03</t>
         </is>
       </c>
     </row>
@@ -636,30 +624,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portal-contribuinte</t>
+          <t>https://wpubirata.elotech.com.br/wp-content/uploads/2025/04/gd_300321113956_bandeira.jpg</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Portal do Contribuinte</t>
-        </is>
-      </c>
+          <t>wpubirata.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://www.ubirata.pr.gov.br/bandeira-e-brasao/</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:00:06</t>
         </is>
       </c>
     </row>
@@ -671,30 +655,26 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/iss/home</t>
+          <t>https://wpubirata.elotech.com.br/wp-content/uploads/2025/04/brasao.jpg</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Nota Fiscal Eletrônica</t>
-        </is>
-      </c>
+          <t>wpubirata.elotech.com.br</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://www.ubirata.pr.gov.br/bandeira-e-brasao/</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:00:06</t>
         </is>
       </c>
     </row>
@@ -706,30 +686,30 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portal-contribuinte/consulta-carne</t>
+          <t>https://www.elotech.com.br/politica-de-privacidade/</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>www.elotech.com.br</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Carnê de IPTU</t>
+          <t>Política de privacidade</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:18</t>
         </is>
       </c>
     </row>
@@ -741,30 +721,30 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/servico-do-esic</t>
+          <t>https://support.google.com/analytics/answer/2799357</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>support.google.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Acesso à Informação</t>
+          <t>https://support.google.com/analytics/answer/2799357</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:18</t>
         </is>
       </c>
     </row>
@@ -776,30 +756,30 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/publicacoes/28/8</t>
+          <t>https://support.google.com/chrome/answer/95647?co=GENIE.Platform%3DDesktop&amp;hl=pt-BR</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>support.google.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Controladoria-Geral do Município</t>
+          <t>Chrome</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:18</t>
         </is>
       </c>
     </row>
@@ -811,30 +791,30 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/ouvidoria</t>
+          <t>https://support.mozilla.org/pt-BR/kb/desative-cookies-terceiros-impedir-rastreamento</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>support.mozilla.org</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ouvidoria</t>
+          <t>Firefox</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:18</t>
         </is>
       </c>
     </row>
@@ -846,30 +826,30 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/governo-digital</t>
+          <t>https://support.microsoft.com/pt-br/help/4027947/microsoft-edge-delete-cookies</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>support.microsoft.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Carta de Serviços ao Usuário</t>
+          <t>Microsoft Edge</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:18</t>
         </is>
       </c>
     </row>
@@ -881,30 +861,30 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/diario-oficial</t>
+          <t>https://support.microsoft.com/pt-br/help/17442/windows-internet-explorer-delete-manage-cookies</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>support.microsoft.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Diário Oficial Eletrônico</t>
+          <t>Internet Explorer</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:18</t>
         </is>
       </c>
     </row>
@@ -916,30 +896,26 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://leismunicipais.com.br/prefeitura/pr/ubirata</t>
+          <t>http://www.keycloak.org</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>leismunicipais.com.br</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Leis Municipais</t>
-        </is>
-      </c>
+          <t>www.keycloak.org</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servidor</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:31</t>
         </is>
       </c>
     </row>
@@ -951,30 +927,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/licitacoes</t>
+          <t>https://elotech.movidesk.com/kb/category/portal-contribuinte</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>elotech.movidesk.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Licitações</t>
+          <t>Confira as novidades da versão</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/portal-contribuinte</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:01:57</t>
         </is>
       </c>
     </row>
@@ -986,30 +962,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/licitacoes-agendamentos-calendario</t>
+          <t>https://elotech.movidesk.com/kb/category/arr-oxy-iss?menuId=33561-91524-0&amp;ticketId=&amp;kbCategoryId=91524</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>elotech.movidesk.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Agenda de Licitações</t>
+          <t>Confira as novidades da versão</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/iss/home</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:02:08</t>
         </is>
       </c>
     </row>
@@ -1021,30 +997,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://ubirata.oxy.elotech.com.br/portaltransparencia/1/publicacoes/41</t>
+          <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2011/lei/l12527.htm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ubirata.oxy.elotech.com.br</t>
+          <t>www.planalto.gov.br</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Processos Seletivos Simplificados</t>
+          <t>12.527/2011</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/servico-do-esic</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:02:25</t>
         </is>
       </c>
     </row>
@@ -1056,26 +1032,30 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/prefeituraubirata/</t>
+          <t>http://leismunicipa.is/18t95</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>leismunicipa.is</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>022/2015</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/servico-do-esic</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:02:25</t>
         </is>
       </c>
     </row>
@@ -1087,26 +1067,30 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/prefeituraubirata/</t>
+          <t>http://leismunicipa.is/0qwrv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
+          <t>leismunicipa.is</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2.826, de 04 de julho de 202</t>
+        </is>
+      </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/solicitacao-de-diaria</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:20:59</t>
         </is>
       </c>
     </row>
@@ -1118,26 +1102,30 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.elotech.com.br</t>
+          <t>https://bvsms.saude.gov.br/bvs/saudelegis/anvisa/2004/res0216_15_09_2004.html</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>www.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
+          <t>bvsms.saude.gov.br</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Resolução 216/2004 - Boas práticas para serviços de Alimentação</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:53</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1149,30 +1137,30 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.vlibras.gov.br/</t>
+          <t>https://www1.tce.pr.gov.br/multimidia/2022/8/docx/00367362.docx</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>www.vlibras.gov.br</t>
+          <t>www1.tce.pr.gov.br</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VLibras</t>
+          <t>Resolução nº 28/2011 - TCE PR</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/acessibilidade</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:54</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1184,26 +1172,30 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://wpubirata.elotech.com.br/wp-content/uploads/2025/04/gd_300321113956_bandeira.jpg</t>
+          <t>https://www.planalto.gov.br/ccivil_03/_ato2015-2018/2018/lei/l13722.htm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>wpubirata.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Lei Federal 13.722 (lei Lucas)</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/bandeira-e-brasao/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:56</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1215,26 +1207,30 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://wpubirata.elotech.com.br/wp-content/uploads/2025/04/brasao.jpg</t>
+          <t>https://www.planalto.gov.br/ccivil_03/_ato2011-2014/2014/lei/l13019.htm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>wpubirata.elotech.com.br</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
+          <t>www.planalto.gov.br</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Lei Federal 13.019/2014</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/bandeira-e-brasao/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-08-04 00:15:56</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1246,22 +1242,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://fadct.selecao.net.br</t>
+          <t>https://www1.tce.pr.gov.br/multimidia/2022/8/docx/00367160.docx</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>fadct.selecao.net.br</t>
+          <t>www1.tce.pr.gov.br</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://fadct.selecao.net.br</t>
+          <t>Instrução Normativa 61/2011 - TCE PR</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/prefeitura-de-ubirata-abre-inscricoes-para-novo-processo-seletivo-simplificado-pss-nesta-terca-feira/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -1269,7 +1265,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-08-04 00:17:38</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1281,30 +1277,30 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://fadct.selecao.net.br/informacoes/46/</t>
+          <t>http://www.controlemunicipal.com.br/inga/sistema/arquivos/46/150317155719_18_pdf.pdf</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>fadct.selecao.net.br</t>
+          <t>www.controlemunicipal.com.br</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://fadct.selecao.net.br</t>
+          <t>Decreto Municipal 18/2017</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/estao-abertas-as-inscricoes-para-processo-seletivo-simplificado-01-2026/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-08-04 00:18:08</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1316,30 +1312,30 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>http://www.aen.pr.gov.br/</t>
+          <t>https://www.documentador.pr.gov.br/documentador/pub.do?action=d&amp;uuid=@gtf-escriba-sesa@b594f615-3817-4a5a-9f17-a103def81830&amp;emPg=true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>www.aen.pr.gov.br</t>
+          <t>www.documentador.pr.gov.br</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>http://www.aen.pr.gov.br</t>
+          <t>Cartilha sobre Boas Práticas para Serviços de Alimentação - RDC 216/2004</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/ubirata-e-um-dos-10-municipios-do-estado-que-tem-seu-proprio-diario-oficial-eletronico/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/social--proposta-para-termo-de-fomento</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-08-04 00:19:12</t>
+          <t>2026-08-04 19:21:18</t>
         </is>
       </c>
     </row>
@@ -1351,30 +1347,30 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>http://www.ingainformatica.com.br/ubirata/concurso/concursos.php</t>
+          <t>http://leis.org/0tfb5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>www.ingainformatica.com.br</t>
+          <t>leis.org</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>www.ingainformatica.com.br/ubirata/concurso/concursos.php</t>
+          <t>Lei Municipal nº 1.817/2010.</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/inscries-para-concurso-iniciam-dia-30/</t>
+          <t>https://ubirata.oxy.elotech.com.br/governo-digital/servicos/solicitacao-de-adiantamento--lei-18172010</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:10</t>
+          <t>2026-08-04 19:28:29</t>
         </is>
       </c>
     </row>
@@ -1386,30 +1382,30 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hashtag/iptu2025?__eep__=6&amp;__cft__[0]=AZXHLo8Z0DYpX5KREIdhYojUgXV9oJvOd_tYyAVQB3IhESvWzUYv3BrdrFMUdb-oiIvfzBcrfW2QcSKFYgx3iCWfzC9RwdVwKy_SmzgE942zxvTrKYmiESfIFA6X4rpWSV5v5oVilOQQdWDYbQjstmLFB8459wGVloec6LaaNrAZ98XZvB2k7BUZNJzCkbnVzo0&amp;__tn__=*NK-R</t>
+          <t>https://fadct.selecao.net.br</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>fadct.selecao.net.br</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>#IPTU2025</t>
+          <t>https://fadct.selecao.net.br</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/iptu-2025-guias-disponveis/</t>
+          <t>https://www.ubirata.pr.gov.br/prefeitura-de-ubirata-abre-inscricoes-para-novo-processo-seletivo-simplificado-pss-nesta-terca-feira/</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:37</t>
+          <t>2026-08-04 19:29:26</t>
         </is>
       </c>
     </row>
@@ -1421,30 +1417,30 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hashtag/prefeituradeubirat%C3%A3?__eep__=6&amp;__cft__[0]=AZXHLo8Z0DYpX5KREIdhYojUgXV9oJvOd_tYyAVQB3IhESvWzUYv3BrdrFMUdb-oiIvfzBcrfW2QcSKFYgx3iCWfzC9RwdVwKy_SmzgE942zxvTrKYmiESfIFA6X4rpWSV5v5oVilOQQdWDYbQjstmLFB8459wGVloec6LaaNrAZ98XZvB2k7BUZNJzCkbnVzo0&amp;__tn__=*NK-R</t>
+          <t>https://fadct.selecao.net.br/informacoes/46/</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>fadct.selecao.net.br</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>#PrefeituraDeUbiratã</t>
+          <t>https://fadct.selecao.net.br</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/iptu-2025-guias-disponveis/</t>
+          <t>https://www.ubirata.pr.gov.br/estao-abertas-as-inscricoes-para-processo-seletivo-simplificado-01-2026/</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-08-04 00:23:37</t>
+          <t>2026-08-04 19:51:29</t>
         </is>
       </c>
     </row>
@@ -1456,30 +1452,30 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>http://www.itde.org.br</t>
+          <t>http://www.aen.pr.gov.br/</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>www.itde.org.br</t>
+          <t>www.aen.pr.gov.br</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>www.itde.org.br</t>
+          <t>http://www.aen.pr.gov.br</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/ultimos-dias-para-inscricao-do-curso-de-pedagogia/</t>
+          <t>https://www.ubirata.pr.gov.br/ubirata-e-um-dos-10-municipios-do-estado-que-tem-seu-proprio-diario-oficial-eletronico/</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-08-04 00:24:27</t>
+          <t>2026-08-04 19:57:17</t>
         </is>
       </c>
     </row>
@@ -1491,30 +1487,30 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://l.facebook.com/l.php?u=http%3A%2F%2Fwww.ubirata.pr.gov.br%2F%3Ffbclid%3DIwAR249kpD74JV1nMbsBbbGSYj_KrqayGQl5kfsikJM91DBKIGyqu80suW6EY_aem_AWEDo_ZjF03-BcN_vZhvcqnHzE9x4g5-Wr9nJgNv6uTrRNe49robXg2gCjowgK589PFseLDO5TxFzkgOukibT6Uz&amp;h=AT0kSBWGxQCJwBMGigch8T07SeQWZgWM2VxWmTKXRLzSZs_5M5q_yEKfNAGLuNRjg61mWMdBL9mEfPzZpwbvKmV-3nuWIoT41q3Tze15xRZCRxeayzCmuHCAiNtf3cPomLkI&amp;__tn__=-UK-R&amp;c[0]=AT2wfgQgSk7E4LCqQF9OyYIftDE2SbqNKzhIYFK_gP9DXr_5dp96y5ytOK4IRY_V2f6q6aRt6SLfkhc2creSlaME7_dWiXthudWwXs1S7yXDT_Rz3HDvd1AvkIq4OAwRUxx1VjsMtbPrxgfoYLbWYeBmOvVrKIlOQ14vaArzH5Wco6A-W7XjQ-c-IJnv73bWBBFy0UNlnvkd</t>
+          <t>http://www.ingainformatica.com.br/ubirata/concurso/concursos.php</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>l.facebook.com</t>
+          <t>www.ingainformatica.com.br</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>www.ubirata.pr.gov.br</t>
+          <t>www.ingainformatica.com.br/ubirata/concurso/concursos.php</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/pss/</t>
+          <t>https://www.ubirata.pr.gov.br/inscries-para-concurso-iniciam-dia-30/</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-08-04 00:25:22</t>
+          <t>2026-08-04 20:14:01</t>
         </is>
       </c>
     </row>
@@ -1526,30 +1522,30 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>http://www.fundacaofafipa.org.br/?fbclid=IwAR0K28JXdU7k4UIoLFlWPXVuLrWTUDuDTp-fWl4AMiLE0H_IN-9JdRqAI9c_aem_AWHoxHtdbmvks3qS9m-iO9aHITJYa9TvHiC16Y6QTorGJfdmNKv8A3Ohs3QzwmXFnq05Gja6wr-Us364XKKZEqOO</t>
+          <t>https://www.facebook.com/hashtag/iptu2025?__eep__=6&amp;__cft__[0]=AZXHLo8Z0DYpX5KREIdhYojUgXV9oJvOd_tYyAVQB3IhESvWzUYv3BrdrFMUdb-oiIvfzBcrfW2QcSKFYgx3iCWfzC9RwdVwKy_SmzgE942zxvTrKYmiESfIFA6X4rpWSV5v5oVilOQQdWDYbQjstmLFB8459wGVloec6LaaNrAZ98XZvB2k7BUZNJzCkbnVzo0&amp;__tn__=*NK-R</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>www.fundacaofafipa.org.br</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>www.fundacaofafipa.org.br.</t>
+          <t>#IPTU2025</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/pss/</t>
+          <t>https://www.ubirata.pr.gov.br/iptu-2025-guias-disponveis/</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-08-04 00:25:22</t>
+          <t>2026-08-04 20:14:27</t>
         </is>
       </c>
     </row>
@@ -1561,30 +1557,30 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://l.facebook.com/l.php?u=http%3A%2F%2Fwww.fundacaofafipa.org.br%2F%3Ffbclid%3DIwAR3irlH9DDw1_sH6uROL2aBEIbqro1TZCK-7VB0IyWEs84Zqkwyzst6NVO0_aem_AWHMpki-U2oJxcdEcVeRxazNzIOPEFceSb5Hr-8IwLkbb5owT8XS6Fs3N6JYownmbC_3sxUgGWoF4i8fKrpDrYg3&amp;h=AT1iD1SnjQx3zcdI1KgNC1TwugZLPq-cp_QraICTzaw67koCWXlSUkIVlmH7-lNeArlpbRB4nlYkYTXzOx7tt-M7VAOsebuALAMQkuQ92YUG7EilgeXm63sJjCWBIEerpwK3&amp;__tn__=-UK-R&amp;c[0]=AT2wfgQgSk7E4LCqQF9OyYIftDE2SbqNKzhIYFK_gP9DXr_5dp96y5ytOK4IRY_V2f6q6aRt6SLfkhc2creSlaME7_dWiXthudWwXs1S7yXDT_Rz3HDvd1AvkIq4OAwRUxx1VjsMtbPrxgfoYLbWYeBmOvVrKIlOQ14vaArzH5Wco6A-W7XjQ-c-IJnv73bWBBFy0UNlnvkd</t>
+          <t>https://www.facebook.com/hashtag/prefeituradeubirat%C3%A3?__eep__=6&amp;__cft__[0]=AZXHLo8Z0DYpX5KREIdhYojUgXV9oJvOd_tYyAVQB3IhESvWzUYv3BrdrFMUdb-oiIvfzBcrfW2QcSKFYgx3iCWfzC9RwdVwKy_SmzgE942zxvTrKYmiESfIFA6X4rpWSV5v5oVilOQQdWDYbQjstmLFB8459wGVloec6LaaNrAZ98XZvB2k7BUZNJzCkbnVzo0&amp;__tn__=*NK-R</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>l.facebook.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>www.fundacaofafipa.org.br.</t>
+          <t>#PrefeituraDeUbiratã</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/pss/</t>
+          <t>https://www.ubirata.pr.gov.br/iptu-2025-guias-disponveis/</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-08-04 00:25:22</t>
+          <t>2026-08-04 20:14:27</t>
         </is>
       </c>
     </row>
@@ -1596,30 +1592,30 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hashtag/dengue?__eep__=6&amp;__cft__[0]=AZUPwpMRJ-rYpbXoadPm52fGCmG2eAzMjQSAuV10T_g0qRRGBUJ8WsE2ui_UTb0oohNTUAKBlEI7A7is_jY46sb1bMglZlqgZplqzxcQNiSQNeEbdfZPe-53LrDHedTvpOESL4nbC030BJz_r5kmyD2YMfCKeotmxrgIbV3Rduuvnee17gP416HOMi195BbXs9k&amp;__tn__=*NK-R</t>
+          <t>http://www.itde.org.br</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>www.itde.org.br</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>#Dengue</t>
+          <t>www.itde.org.br</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/a-luta-contra-a-dengue-nossa/</t>
+          <t>https://www.ubirata.pr.gov.br/ultimos-dias-para-inscricao-do-curso-de-pedagogia/</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:16</t>
+          <t>2026-08-04 20:15:21</t>
         </is>
       </c>
     </row>
@@ -1631,30 +1627,30 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hashtag/preven%C3%A7%C3%A3o?__eep__=6&amp;__cft__[0]=AZUPwpMRJ-rYpbXoadPm52fGCmG2eAzMjQSAuV10T_g0qRRGBUJ8WsE2ui_UTb0oohNTUAKBlEI7A7is_jY46sb1bMglZlqgZplqzxcQNiSQNeEbdfZPe-53LrDHedTvpOESL4nbC030BJz_r5kmyD2YMfCKeotmxrgIbV3Rduuvnee17gP416HOMi195BbXs9k&amp;__tn__=*NK-R</t>
+          <t>https://l.facebook.com/l.php?u=http%3A%2F%2Fwww.ubirata.pr.gov.br%2F%3Ffbclid%3DIwAR249kpD74JV1nMbsBbbGSYj_KrqayGQl5kfsikJM91DBKIGyqu80suW6EY_aem_AWEDo_ZjF03-BcN_vZhvcqnHzE9x4g5-Wr9nJgNv6uTrRNe49robXg2gCjowgK589PFseLDO5TxFzkgOukibT6Uz&amp;h=AT0kSBWGxQCJwBMGigch8T07SeQWZgWM2VxWmTKXRLzSZs_5M5q_yEKfNAGLuNRjg61mWMdBL9mEfPzZpwbvKmV-3nuWIoT41q3Tze15xRZCRxeayzCmuHCAiNtf3cPomLkI&amp;__tn__=-UK-R&amp;c[0]=AT2wfgQgSk7E4LCqQF9OyYIftDE2SbqNKzhIYFK_gP9DXr_5dp96y5ytOK4IRY_V2f6q6aRt6SLfkhc2creSlaME7_dWiXthudWwXs1S7yXDT_Rz3HDvd1AvkIq4OAwRUxx1VjsMtbPrxgfoYLbWYeBmOvVrKIlOQ14vaArzH5Wco6A-W7XjQ-c-IJnv73bWBBFy0UNlnvkd</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>l.facebook.com</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>#Prevenção</t>
+          <t>www.ubirata.pr.gov.br</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/a-luta-contra-a-dengue-nossa/</t>
+          <t>https://www.ubirata.pr.gov.br/pss/</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:16</t>
+          <t>2026-08-04 20:16:13</t>
         </is>
       </c>
     </row>
@@ -1666,30 +1662,30 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hashtag/sa%C3%BAde?__eep__=6&amp;__cft__[0]=AZUPwpMRJ-rYpbXoadPm52fGCmG2eAzMjQSAuV10T_g0qRRGBUJ8WsE2ui_UTb0oohNTUAKBlEI7A7is_jY46sb1bMglZlqgZplqzxcQNiSQNeEbdfZPe-53LrDHedTvpOESL4nbC030BJz_r5kmyD2YMfCKeotmxrgIbV3Rduuvnee17gP416HOMi195BbXs9k&amp;__tn__=*NK-R</t>
+          <t>http://www.fundacaofafipa.org.br/?fbclid=IwAR0K28JXdU7k4UIoLFlWPXVuLrWTUDuDTp-fWl4AMiLE0H_IN-9JdRqAI9c_aem_AWHoxHtdbmvks3qS9m-iO9aHITJYa9TvHiC16Y6QTorGJfdmNKv8A3Ohs3QzwmXFnq05Gja6wr-Us364XKKZEqOO</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>www.fundacaofafipa.org.br</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>#Saúde</t>
+          <t>www.fundacaofafipa.org.br.</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/a-luta-contra-a-dengue-nossa/</t>
+          <t>https://www.ubirata.pr.gov.br/pss/</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:16</t>
+          <t>2026-08-04 20:16:13</t>
         </is>
       </c>
     </row>
@@ -1701,30 +1697,30 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/explore/tags/escolinhadefutebol/</t>
+          <t>https://l.facebook.com/l.php?u=http%3A%2F%2Fwww.fundacaofafipa.org.br%2F%3Ffbclid%3DIwAR3irlH9DDw1_sH6uROL2aBEIbqro1TZCK-7VB0IyWEs84Zqkwyzst6NVO0_aem_AWHMpki-U2oJxcdEcVeRxazNzIOPEFceSb5Hr-8IwLkbb5owT8XS6Fs3N6JYownmbC_3sxUgGWoF4i8fKrpDrYg3&amp;h=AT1iD1SnjQx3zcdI1KgNC1TwugZLPq-cp_QraICTzaw67koCWXlSUkIVlmH7-lNeArlpbRB4nlYkYTXzOx7tt-M7VAOsebuALAMQkuQ92YUG7EilgeXm63sJjCWBIEerpwK3&amp;__tn__=-UK-R&amp;c[0]=AT2wfgQgSk7E4LCqQF9OyYIftDE2SbqNKzhIYFK_gP9DXr_5dp96y5ytOK4IRY_V2f6q6aRt6SLfkhc2creSlaME7_dWiXthudWwXs1S7yXDT_Rz3HDvd1AvkIq4OAwRUxx1VjsMtbPrxgfoYLbWYeBmOvVrKIlOQ14vaArzH5Wco6A-W7XjQ-c-IJnv73bWBBFy0UNlnvkd</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
+          <t>l.facebook.com</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>#EscolinhaDeFutebol</t>
+          <t>www.fundacaofafipa.org.br.</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
+          <t>https://www.ubirata.pr.gov.br/pss/</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:19</t>
+          <t>2026-08-04 20:16:13</t>
         </is>
       </c>
     </row>
@@ -1736,22 +1732,22 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/explore/tags/cascavel/</t>
+          <t>https://www.facebook.com/hashtag/dengue?__eep__=6&amp;__cft__[0]=AZUPwpMRJ-rYpbXoadPm52fGCmG2eAzMjQSAuV10T_g0qRRGBUJ8WsE2ui_UTb0oohNTUAKBlEI7A7is_jY46sb1bMglZlqgZplqzxcQNiSQNeEbdfZPe-53LrDHedTvpOESL4nbC030BJz_r5kmyD2YMfCKeotmxrgIbV3Rduuvnee17gP416HOMi195BbXs9k&amp;__tn__=*NK-R</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>#Cascavel</t>
+          <t>#Dengue</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
+          <t>https://www.ubirata.pr.gov.br/a-luta-contra-a-dengue-nossa/</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -1759,7 +1755,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:19</t>
+          <t>2026-08-04 20:17:11</t>
         </is>
       </c>
     </row>
@@ -1771,22 +1767,22 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/explore/tags/ubirat%C3%A3/</t>
+          <t>https://www.facebook.com/hashtag/preven%C3%A7%C3%A3o?__eep__=6&amp;__cft__[0]=AZUPwpMRJ-rYpbXoadPm52fGCmG2eAzMjQSAuV10T_g0qRRGBUJ8WsE2ui_UTb0oohNTUAKBlEI7A7is_jY46sb1bMglZlqgZplqzxcQNiSQNeEbdfZPe-53LrDHedTvpOESL4nbC030BJz_r5kmyD2YMfCKeotmxrgIbV3Rduuvnee17gP416HOMi195BbXs9k&amp;__tn__=*NK-R</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>#Ubiratã</t>
+          <t>#Prevenção</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
+          <t>https://www.ubirata.pr.gov.br/a-luta-contra-a-dengue-nossa/</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -1794,7 +1790,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:19</t>
+          <t>2026-08-04 20:17:11</t>
         </is>
       </c>
     </row>
@@ -1806,22 +1802,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/explore/tags/esporteparatodos/</t>
+          <t>https://www.facebook.com/hashtag/sa%C3%BAde?__eep__=6&amp;__cft__[0]=AZUPwpMRJ-rYpbXoadPm52fGCmG2eAzMjQSAuV10T_g0qRRGBUJ8WsE2ui_UTb0oohNTUAKBlEI7A7is_jY46sb1bMglZlqgZplqzxcQNiSQNeEbdfZPe-53LrDHedTvpOESL4nbC030BJz_r5kmyD2YMfCKeotmxrgIbV3Rduuvnee17gP416HOMi195BbXs9k&amp;__tn__=*NK-R</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>www.instagram.com</t>
+          <t>www.facebook.com</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>#EsporteParaTodos</t>
+          <t>#Saúde</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
+          <t>https://www.ubirata.pr.gov.br/a-luta-contra-a-dengue-nossa/</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:19</t>
+          <t>2026-08-04 20:17:11</t>
         </is>
       </c>
     </row>
@@ -1841,7 +1837,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/explore/tags/inscri%C3%A7%C3%B5esabertas/</t>
+          <t>https://www.instagram.com/explore/tags/escolinhadefutebol/</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1851,7 +1847,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>#inscriçõesabertas</t>
+          <t>#EscolinhaDeFutebol</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -1864,7 +1860,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:19</t>
+          <t>2026-08-04 20:17:15</t>
         </is>
       </c>
     </row>
@@ -1876,22 +1872,22 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.gov.br/saude/pt-br/composicao/seidigi/meu-sus-digital?fbclid=IwAR35Quvd1Opg89HtRcPeVzM2Qg-JgKwfW2v-bEAfU-mJ9T1r3vERPXSJ168</t>
+          <t>https://www.instagram.com/explore/tags/cascavel/</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>www.gov.br</t>
+          <t>www.instagram.com</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>https://www.gov.br/…/composicao/seidigi/meu-sus-digital</t>
+          <t>#Cascavel</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/mulheres-e-meninas-em-situao-de-vulnerabilidade-podem-retirar-absorventes-de-forma-gratuita-na-rede-de-farmcia-popular/</t>
+          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -1899,7 +1895,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:21</t>
+          <t>2026-08-04 20:17:15</t>
         </is>
       </c>
     </row>
@@ -1911,22 +1907,22 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.facebook.com/hashtag/ubirat%C3%A3%C3%A9issoa%C3%AD?__eep__=6&amp;__cft__[0]=AZWgUA5u7UpPMHxYVRRS9AThHs7A9N-Huq8vAYlQ9PT2JW0Dul2d22-RnjZcN4Wpzkh-Lk7AkBmg8Z3kmjb2NtW4q6eotZgr2HPtO0opu_xOtim4nbxCV9BqAwq0AuMT_5gO4PEs_ldDWYSKwAq_Bs-pPSc4ZFynmzYRD2c6Du6rjuihwOHMAJiTqUYugaNBGuM&amp;__tn__=*NK-R</t>
+          <t>https://www.instagram.com/explore/tags/ubirat%C3%A3/</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>www.facebook.com</t>
+          <t>www.instagram.com</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>#UBIRATÃÉISSOAÍ</t>
+          <t>#Ubiratã</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/programa-de-conservao-de-estradas/</t>
+          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -1934,7 +1930,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:24</t>
+          <t>2026-08-04 20:17:15</t>
         </is>
       </c>
     </row>
@@ -1946,22 +1942,22 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>http://www.exatuspr.com.br/</t>
+          <t>https://www.instagram.com/explore/tags/esporteparatodos/</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>www.exatuspr.com.br</t>
+          <t>www.instagram.com</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>www.exatuspr.com.br</t>
+          <t>#EsporteParaTodos</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>https://www.ubirata.pr.gov.br/publicada-a-lista-de-aprovados-no-concurso-de-ubirata-2/</t>
+          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -1969,7 +1965,147 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-08-04 00:26:53</t>
+          <t>2026-08-04 20:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/explore/tags/inscri%C3%A7%C3%B5esabertas/</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>www.instagram.com</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>#inscriçõesabertas</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/oportunidade-imperdvel-para-crianas-e-adolescentes-de-ubirat/</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>10</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:17:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/saude/pt-br/composicao/seidigi/meu-sus-digital?fbclid=IwAR35Quvd1Opg89HtRcPeVzM2Qg-JgKwfW2v-bEAfU-mJ9T1r3vERPXSJ168</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>www.gov.br</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>https://www.gov.br/…/composicao/seidigi/meu-sus-digital</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/mulheres-e-meninas-em-situao-de-vulnerabilidade-podem-retirar-absorventes-de-forma-gratuita-na-rede-de-farmcia-popular/</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>10</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:17:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/hashtag/ubirat%C3%A3%C3%A9issoa%C3%AD?__eep__=6&amp;__cft__[0]=AZWgUA5u7UpPMHxYVRRS9AThHs7A9N-Huq8vAYlQ9PT2JW0Dul2d22-RnjZcN4Wpzkh-Lk7AkBmg8Z3kmjb2NtW4q6eotZgr2HPtO0opu_xOtim4nbxCV9BqAwq0AuMT_5gO4PEs_ldDWYSKwAq_Bs-pPSc4ZFynmzYRD2c6Du6rjuihwOHMAJiTqUYugaNBGuM&amp;__tn__=*NK-R</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>www.facebook.com</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>#UBIRATÃÉISSOAÍ</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/programa-de-conservao-de-estradas/</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>10</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:17:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>ubirata</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>http://www.exatuspr.com.br/</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>www.exatuspr.com.br</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>www.exatuspr.com.br</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>https://www.ubirata.pr.gov.br/publicada-a-lista-de-aprovados-no-concurso-de-ubirata-2/</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>10</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>2026-08-04 20:17:49</t>
         </is>
       </c>
     </row>
